--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -630,40 +630,40 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>4875.04189130478</v>
+        <v>4629.139016586378</v>
       </c>
       <c r="E2">
-        <v>4896.897017089668</v>
+        <v>4651.355208234036</v>
       </c>
       <c r="F2">
-        <v>4914.082579224293</v>
+        <v>4668.529798229674</v>
       </c>
       <c r="G2">
-        <v>385.7142701331063</v>
+        <v>369.8529166826939</v>
       </c>
       <c r="H2">
-        <v>7.849161342217263</v>
+        <v>7.922256741789324</v>
       </c>
       <c r="I2">
-        <v>4206.436481143591</v>
+        <v>3990.989096395166</v>
       </c>
       <c r="J2">
-        <v>4534.016533692296</v>
+        <v>4304.432851284701</v>
       </c>
       <c r="K2">
-        <v>5294.617632655409</v>
+        <v>5032.580210046819</v>
       </c>
       <c r="L2">
-        <v>5720.738297166202</v>
+        <v>5442.389715932903</v>
       </c>
       <c r="M2">
-        <v>-14.09996031234557</v>
+        <v>-14.19728406615475</v>
       </c>
       <c r="N2">
-        <v>16.82374118143413</v>
+        <v>17.00653835893984</v>
       </c>
       <c r="O2">
-        <v>0.03228632938903961</v>
+        <v>0.03372019957344529</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -677,40 +677,40 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>5595.226019299745</v>
+        <v>4261.281022540152</v>
       </c>
       <c r="E3">
-        <v>5592.109923394642</v>
+        <v>4259.162191257918</v>
       </c>
       <c r="F3">
-        <v>5613.951637833751</v>
+        <v>4275.801191769181</v>
       </c>
       <c r="G3">
-        <v>468.334733174163</v>
+        <v>356.1667648625975</v>
       </c>
       <c r="H3">
-        <v>8.342336439415405</v>
+        <v>8.32982519271968</v>
       </c>
       <c r="I3">
-        <v>4753.210809916976</v>
+        <v>3621.269076316772</v>
       </c>
       <c r="J3">
-        <v>5151.527875401826</v>
+        <v>3924.37894030944</v>
       </c>
       <c r="K3">
-        <v>6077.531680528639</v>
+        <v>4628.31077990047</v>
       </c>
       <c r="L3">
-        <v>6589.588283121095</v>
+        <v>5017.491585606876</v>
       </c>
       <c r="M3">
-        <v>-15.00147752761661</v>
+        <v>-14.97696228263963</v>
       </c>
       <c r="N3">
-        <v>17.83724521496783</v>
+        <v>17.80466111164905</v>
       </c>
       <c r="O3">
-        <v>0.04240520379477204</v>
+        <v>0.04250637541064802</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -724,40 +724,40 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>43.01963532551069</v>
+        <v>95.51845307556377</v>
       </c>
       <c r="E4">
-        <v>42.994880399202</v>
+        <v>95.45468832677814</v>
       </c>
       <c r="F4">
-        <v>43.16286728350229</v>
+        <v>95.82719494375063</v>
       </c>
       <c r="G4">
-        <v>3.60248595115065</v>
+        <v>8.017561729515547</v>
       </c>
       <c r="H4">
-        <v>8.34626190954555</v>
+        <v>8.366687279348787</v>
       </c>
       <c r="I4">
-        <v>36.54410721311837</v>
+        <v>81.10242947302176</v>
       </c>
       <c r="J4">
-        <v>39.60609344840805</v>
+        <v>87.91022568826547</v>
       </c>
       <c r="K4">
-        <v>46.72860488355031</v>
+        <v>103.7533883649353</v>
       </c>
       <c r="L4">
-        <v>50.66887478673794</v>
+        <v>112.5260073444621</v>
       </c>
       <c r="M4">
-        <v>-15.00358444119165</v>
+        <v>-15.03567724680329</v>
       </c>
       <c r="N4">
-        <v>17.84862364142865</v>
+        <v>17.8842122025922</v>
       </c>
       <c r="O4">
-        <v>0.04234514363284922</v>
+        <v>0.04252884922528793</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -771,40 +771,40 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>3833.21048095657</v>
+        <v>4855.583327817173</v>
       </c>
       <c r="E5">
-        <v>3830.350117713157</v>
+        <v>4851.906633386088</v>
       </c>
       <c r="F5">
-        <v>3845.365870643727</v>
+        <v>4870.961891764669</v>
       </c>
       <c r="G5">
-        <v>322.2345629113504</v>
+        <v>408.2190442544017</v>
       </c>
       <c r="H5">
-        <v>8.37981543892486</v>
+        <v>8.380665940839679</v>
       </c>
       <c r="I5">
-        <v>3253.610725387616</v>
+        <v>4121.369138332022</v>
       </c>
       <c r="J5">
-        <v>3527.158658795715</v>
+        <v>4467.788669920978</v>
       </c>
       <c r="K5">
-        <v>4163.841755519727</v>
+        <v>5274.424314824582</v>
       </c>
       <c r="L5">
-        <v>4516.875876954976</v>
+        <v>5721.682126200532</v>
       </c>
       <c r="M5">
-        <v>-15.05709333615363</v>
+        <v>-15.05670966599439</v>
       </c>
       <c r="N5">
-        <v>17.92331609758164</v>
+        <v>17.92646805751574</v>
       </c>
       <c r="O5">
-        <v>0.04191351114457256</v>
+        <v>0.04195994547778891</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -818,40 +818,40 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>1481.801246893921</v>
+        <v>259.4180916719396</v>
       </c>
       <c r="E6">
-        <v>1480.985779071771</v>
+        <v>259.5600341016295</v>
       </c>
       <c r="F6">
-        <v>1486.548531981589</v>
+        <v>260.3077093241529</v>
       </c>
       <c r="G6">
-        <v>120.9036385725364</v>
+        <v>18.67591642389523</v>
       </c>
       <c r="H6">
-        <v>8.133178027586508</v>
+        <v>7.174553712751821</v>
       </c>
       <c r="I6">
-        <v>1264.854093505056</v>
+        <v>225.7479612598866</v>
       </c>
       <c r="J6">
-        <v>1366.978960560977</v>
+        <v>241.8370425346428</v>
       </c>
       <c r="K6">
-        <v>1606.325083642944</v>
+        <v>278.8216539275084</v>
       </c>
       <c r="L6">
-        <v>1738.713686227722</v>
+        <v>299.1378075950564</v>
       </c>
       <c r="M6">
-        <v>-14.59377183906373</v>
+        <v>-13.02668685445773</v>
       </c>
       <c r="N6">
-        <v>17.40245657979818</v>
+        <v>15.24802292094412</v>
       </c>
       <c r="O6">
-        <v>0.04165171706827474</v>
+        <v>0.03720502433586995</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -865,40 +865,40 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>4875.04189130478</v>
+        <v>4629.139016586378</v>
       </c>
       <c r="E7">
-        <v>3843.903312778215</v>
+        <v>3557.805652650764</v>
       </c>
       <c r="F7">
-        <v>3876.424722553788</v>
+        <v>3593.199556803037</v>
       </c>
       <c r="G7">
-        <v>390.7413812394806</v>
+        <v>383.719582755758</v>
       </c>
       <c r="H7">
-        <v>10.07994245228269</v>
+        <v>10.679050152649</v>
       </c>
       <c r="I7">
-        <v>3205.645985311821</v>
+        <v>2940.766199459483</v>
       </c>
       <c r="J7">
-        <v>3497.142123024981</v>
+        <v>3221.110220188275</v>
       </c>
       <c r="K7">
-        <v>4253.810020790544</v>
+        <v>3962.302274814746</v>
       </c>
       <c r="L7">
-        <v>4741.386845515559</v>
+        <v>4449.461140125159</v>
       </c>
       <c r="M7">
-        <v>-16.60440639452733</v>
+        <v>-17.34325911623509</v>
       </c>
       <c r="N7">
-        <v>23.34823380582587</v>
+        <v>25.06195038534669</v>
       </c>
       <c r="O7">
-        <v>0.03824765848755188</v>
+        <v>0.03620472748441337</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -912,40 +912,40 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>5595.226019299745</v>
+        <v>4261.281022540152</v>
       </c>
       <c r="E8">
-        <v>2642.643074200229</v>
+        <v>2397.939093358254</v>
       </c>
       <c r="F8">
-        <v>2677.549159570194</v>
+        <v>2417.958614580572</v>
       </c>
       <c r="G8">
-        <v>318.1183252080793</v>
+        <v>246.6248454324626</v>
       </c>
       <c r="H8">
-        <v>11.88095180516291</v>
+        <v>10.19971325999072</v>
       </c>
       <c r="I8">
-        <v>2151.964800680243</v>
+        <v>1991.618823758696</v>
       </c>
       <c r="J8">
-        <v>2375.082177943172</v>
+        <v>2178.966115341834</v>
       </c>
       <c r="K8">
-        <v>2976.171040719429</v>
+        <v>2655.505501467193</v>
       </c>
       <c r="L8">
-        <v>3402.729538983468</v>
+        <v>2958.63092262199</v>
       </c>
       <c r="M8">
-        <v>-18.56770890894851</v>
+        <v>-16.94456171655786</v>
       </c>
       <c r="N8">
-        <v>28.76235811804706</v>
+        <v>23.38223814010643</v>
       </c>
       <c r="O8">
-        <v>0.05642306500953551</v>
+        <v>0.04649620794505965</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -959,40 +959,40 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>43.01963532551069</v>
+        <v>95.51845307556377</v>
       </c>
       <c r="E9">
-        <v>32.67764753314299</v>
+        <v>70.88990789404747</v>
       </c>
       <c r="F9">
-        <v>32.91677430424717</v>
+        <v>71.42288401169881</v>
       </c>
       <c r="G9">
-        <v>6.55666437501051</v>
+        <v>15.38647510284305</v>
       </c>
       <c r="H9">
-        <v>19.9189152448772</v>
+        <v>21.54278046280349</v>
       </c>
       <c r="I9">
-        <v>21.98488650772371</v>
+        <v>45.93243271448221</v>
       </c>
       <c r="J9">
-        <v>25.71129515985265</v>
+        <v>54.37214198274688</v>
       </c>
       <c r="K9">
-        <v>40.04507602866691</v>
+        <v>88.25993698408881</v>
       </c>
       <c r="L9">
-        <v>45.48526402773383</v>
+        <v>100.6241641490363</v>
       </c>
       <c r="M9">
-        <v>-32.72194246716887</v>
+        <v>-35.20596361454844</v>
       </c>
       <c r="N9">
-        <v>39.19381430869782</v>
+        <v>41.9442726592759</v>
       </c>
       <c r="O9">
-        <v>0.09971597307986367</v>
+        <v>0.1081542795426334</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1006,40 +1006,40 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>3833.21048095657</v>
+        <v>4855.583327817173</v>
       </c>
       <c r="E10">
-        <v>2983.865230031622</v>
+        <v>3961.772006685232</v>
       </c>
       <c r="F10">
-        <v>3005.672069973584</v>
+        <v>3990.071165559074</v>
       </c>
       <c r="G10">
-        <v>548.0389444101303</v>
+        <v>610.6449435575681</v>
       </c>
       <c r="H10">
-        <v>18.23349093485594</v>
+        <v>15.30411158649114</v>
       </c>
       <c r="I10">
-        <v>2082.484494744479</v>
+        <v>2939.171068356145</v>
       </c>
       <c r="J10">
-        <v>2410.552610410687</v>
+        <v>3342.091747790692</v>
       </c>
       <c r="K10">
-        <v>3593.953547438095</v>
+        <v>4633.532435036369</v>
       </c>
       <c r="L10">
-        <v>4076.56112470845</v>
+        <v>5211.684516676283</v>
       </c>
       <c r="M10">
-        <v>-30.20849354103001</v>
+        <v>-25.81170588826197</v>
       </c>
       <c r="N10">
-        <v>36.62014904960196</v>
+        <v>31.54932964042114</v>
       </c>
       <c r="O10">
-        <v>0.08477401790934334</v>
+        <v>0.07160027093183655</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1053,40 +1053,40 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>1481.801246893921</v>
+        <v>259.4180916719396</v>
       </c>
       <c r="E11">
-        <v>1124.675330428039</v>
+        <v>216.1736775271942</v>
       </c>
       <c r="F11">
-        <v>1132.783159202988</v>
+        <v>217.3822134490496</v>
       </c>
       <c r="G11">
-        <v>223.8287015702132</v>
+        <v>29.0786386413359</v>
       </c>
       <c r="H11">
-        <v>19.75918336636433</v>
+        <v>13.37673316503946</v>
       </c>
       <c r="I11">
-        <v>760.0465531728173</v>
+        <v>167.4231525537851</v>
       </c>
       <c r="J11">
-        <v>885.751412071479</v>
+        <v>186.4274030481546</v>
       </c>
       <c r="K11">
-        <v>1374.68841710103</v>
+        <v>248.2257348088353</v>
       </c>
       <c r="L11">
-        <v>1562.370943048976</v>
+        <v>275.0192199817689</v>
       </c>
       <c r="M11">
-        <v>-32.42080335455106</v>
+        <v>-22.55155462545912</v>
       </c>
       <c r="N11">
-        <v>38.91750808247518</v>
+        <v>27.221418966318</v>
       </c>
       <c r="O11">
-        <v>0.1138490672574221</v>
+        <v>0.07939984160304175</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1118,7 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>88.68829432113078</v>
+        <v>86.32184887666588</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1129,7 +1129,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>0.115177381854156</v>
+        <v>0.1068499362635191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>0.009184947311505183</v>
+        <v>0.009881777646257202</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1151,7 +1151,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.002019099593190505</v>
+        <v>0.002234438596120387</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1162,7 +1162,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>5.295818214354771</v>
+        <v>5.86062255477616</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1173,7 +1173,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>5.889506035755611</v>
+        <v>7.698562416052061</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1184,7 +1184,7 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>99.98475382922869</v>
+        <v>99.97363589809672</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1228,7 +1228,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0.005533432102393437</v>
+        <v>0.00956856446188631</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1239,7 +1239,7 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>0.00971273866892979</v>
+        <v>0.01679553744138497</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1250,7 +1250,7 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>99.98734056478081</v>
+        <v>99.99744441935184</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1294,7 +1294,7 @@
         <v>32</v>
       </c>
       <c r="C18">
-        <v>0.004292111699724438</v>
+        <v>0.0008664555258324851</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1305,7 +1305,7 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>0.0083673235194605</v>
+        <v>0.001689125122333169</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1316,7 +1316,7 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>99.99986368173508</v>
+        <v>99.99991506020071</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1360,7 +1360,7 @@
         <v>32</v>
       </c>
       <c r="C24">
-        <v>4.967661325333097E-05</v>
+        <v>3.095345705543773E-05</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1371,7 +1371,7 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>8.66416516644192E-05</v>
+        <v>5.398634223171339E-05</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1382,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>99.87091775172587</v>
+        <v>95.14012854415468</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1393,7 +1393,7 @@
         <v>29</v>
       </c>
       <c r="C27">
-        <v>0.1290822482741301</v>
+        <v>4.859871455845328</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1521,13 +1521,13 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.00017</v>
+        <v>0.00018</v>
       </c>
       <c r="E4">
-        <v>0.06095</v>
+        <v>0.54589</v>
       </c>
       <c r="F4">
-        <v>0.67158</v>
+        <v>0.05353</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1544,10 +1544,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.93888</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0.06112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1581,10 +1581,10 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>0.99983</v>
+        <v>0.99982</v>
       </c>
       <c r="E7">
-        <v>0.00017</v>
+        <v>0.00018</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1604,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.45393</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.5460700000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.4004</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.2673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1844,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>0.03318</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.91403</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>0.05279</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.08597</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0.91403</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>0.01932</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2421,13 +2421,13 @@
         <v>40</v>
       </c>
       <c r="D49">
-        <v>0.05759</v>
+        <v>0.41399</v>
       </c>
       <c r="E49">
-        <v>0.45378</v>
+        <v>0.16194</v>
       </c>
       <c r="F49">
-        <v>0.29634</v>
+        <v>0.15045</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2441,13 +2441,13 @@
         <v>41</v>
       </c>
       <c r="D50">
-        <v>0.85414</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.14013</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>0.00573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2481,13 +2481,13 @@
         <v>43</v>
       </c>
       <c r="D52">
-        <v>0.08827</v>
+        <v>0.32811</v>
       </c>
       <c r="E52">
-        <v>0.29118</v>
+        <v>0.11883</v>
       </c>
       <c r="F52">
-        <v>0.22851</v>
+        <v>0.08807</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2501,13 +2501,13 @@
         <v>44</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>0.2579</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>0.50717</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>0.23493</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2524,10 +2524,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>0.21206</v>
       </c>
       <c r="F54">
-        <v>0.00209</v>
+        <v>0.50723</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2544,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0.11491</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>0.46733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2621,13 +2621,13 @@
         <v>41</v>
       </c>
       <c r="D59">
-        <v>0.88797</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0.11203</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>0.07764</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2661,13 +2661,13 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.11203</v>
+        <v>0.00057</v>
       </c>
       <c r="E61">
-        <v>0.20542</v>
+        <v>0.35161</v>
       </c>
       <c r="F61">
-        <v>0.5727</v>
+        <v>0.57018</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>0.64782</v>
       </c>
       <c r="F62">
-        <v>0.10985</v>
+        <v>0.35218</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2721,13 +2721,13 @@
         <v>46</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>0.99943</v>
       </c>
       <c r="E64">
-        <v>0.68255</v>
+        <v>0.00057</v>
       </c>
       <c r="F64">
-        <v>0.31745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2741,13 +2741,13 @@
         <v>38</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>0.24605</v>
       </c>
       <c r="E65">
-        <v>0.1526</v>
+        <v>0.75395</v>
       </c>
       <c r="F65">
-        <v>0.8474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2801,10 +2801,10 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.15939</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>0.84061</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2841,13 +2841,13 @@
         <v>43</v>
       </c>
       <c r="D70">
-        <v>0.84061</v>
+        <v>0.75395</v>
       </c>
       <c r="E70">
-        <v>0.00679</v>
+        <v>0.19277</v>
       </c>
       <c r="F70">
-        <v>0.1526</v>
+        <v>0.05328</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>0.05328</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>0.94672</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2921,10 +2921,10 @@
         <v>38</v>
       </c>
       <c r="D74">
-        <v>0.18316</v>
+        <v>0.73704</v>
       </c>
       <c r="E74">
-        <v>0.81684</v>
+        <v>0.26296</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2984,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0.15698</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>0.84302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3021,13 +3021,13 @@
         <v>43</v>
       </c>
       <c r="D79">
-        <v>0.81684</v>
+        <v>0.26296</v>
       </c>
       <c r="E79">
-        <v>0.02618</v>
+        <v>0.50726</v>
       </c>
       <c r="F79">
-        <v>0.11224</v>
+        <v>0.22978</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>0.22978</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>0.77022</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>0.04474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>0.24611</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3161,10 +3161,10 @@
         <v>41</v>
       </c>
       <c r="D86">
-        <v>0.16707</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>0.8329299999999999</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3181,13 +3181,13 @@
         <v>42</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>0.31542</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>0.61151</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>0.04639</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3201,13 +3201,13 @@
         <v>43</v>
       </c>
       <c r="D88">
-        <v>0.8329299999999999</v>
+        <v>0.66331</v>
       </c>
       <c r="E88">
-        <v>0.06718</v>
+        <v>0.08656999999999999</v>
       </c>
       <c r="F88">
-        <v>0.09989000000000001</v>
+        <v>0.02326</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>0.00023</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3261,13 +3261,13 @@
         <v>46</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>0.02127</v>
       </c>
       <c r="E91">
-        <v>0.09989000000000001</v>
+        <v>0.29472</v>
       </c>
       <c r="F91">
-        <v>0.90011</v>
+        <v>0.68401</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3305,7 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>4902.509428209002</v>
+        <v>4656.250204226273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>5596.344978159629</v>
+        <v>4262.552479823979</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>43.02592266453101</v>
+        <v>95.51884731880483</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>3832.634163596104</v>
+        <v>4854.862058366974</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>1481.866326197503</v>
+        <v>259.6597667377461</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4902.509428209002</v>
+        <v>4656.250204226273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>5596.344978159629</v>
+        <v>4262.552479823979</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>43.02592266453101</v>
+        <v>95.51884731880483</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>20</v>
       </c>
       <c r="D10">
-        <v>3832.634163596104</v>
+        <v>4854.862058366974</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3431,7 +3431,7 @@
         <v>21</v>
       </c>
       <c r="D11">
-        <v>763.5840600281023</v>
+        <v>151.3560380952445</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>17</v>
       </c>
       <c r="D12">
-        <v>4902.509428209002</v>
+        <v>4656.250204226273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3459,7 +3459,7 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>5596.344978159629</v>
+        <v>4262.552479823979</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3473,7 +3473,7 @@
         <v>19</v>
       </c>
       <c r="D14">
-        <v>43.02592266453101</v>
+        <v>95.51884731880483</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3487,7 +3487,7 @@
         <v>20</v>
       </c>
       <c r="D15">
-        <v>3832.634163596104</v>
+        <v>4854.862058366974</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>21</v>
       </c>
       <c r="D16">
-        <v>2917.931937455814</v>
+        <v>476.2593151098142</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>4778.947778584594</v>
+        <v>4539.579626043395</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3529,7 +3529,7 @@
         <v>18</v>
       </c>
       <c r="D18">
-        <v>5429.388175840547</v>
+        <v>4135.47464587318</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3543,7 +3543,7 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>41.74092925616684</v>
+        <v>92.65953114599043</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3557,7 +3557,7 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>3717.69228006517</v>
+        <v>4709.269371156532</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3571,7 +3571,7 @@
         <v>21</v>
       </c>
       <c r="D21">
-        <v>1438.741947464408</v>
+        <v>253.1539457184531</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>17</v>
       </c>
       <c r="D22">
-        <v>4778.947778584594</v>
+        <v>4539.579626043395</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3599,7 +3599,7 @@
         <v>18</v>
       </c>
       <c r="D23">
-        <v>5429.388175840547</v>
+        <v>4135.47464587318</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3613,7 +3613,7 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>41.74092925616684</v>
+        <v>92.65953114599043</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3627,7 +3627,7 @@
         <v>20</v>
       </c>
       <c r="D25">
-        <v>3717.69228006517</v>
+        <v>4709.269371156532</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3641,7 +3641,7 @@
         <v>21</v>
       </c>
       <c r="D26">
-        <v>742.0532357199764</v>
+        <v>148.0944792739415</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>4778.947778584594</v>
+        <v>4539.579626043395</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3669,7 +3669,7 @@
         <v>18</v>
       </c>
       <c r="D28">
-        <v>5429.388175840547</v>
+        <v>4135.47464587318</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3683,7 +3683,7 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>41.74092925616684</v>
+        <v>92.65953114599043</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3697,7 +3697,7 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>3717.69228006517</v>
+        <v>4709.269371156532</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3711,7 +3711,7 @@
         <v>21</v>
       </c>
       <c r="D31">
-        <v>2831.744285026749</v>
+        <v>463.2447567701117</v>
       </c>
     </row>
   </sheetData>
@@ -3746,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4902.795512543069</v>
+        <v>4656.511483455182</v>
       </c>
       <c r="C2">
-        <v>4234.582283294772</v>
+        <v>4024.174273137617</v>
       </c>
       <c r="D2">
-        <v>5679.156380429015</v>
+        <v>5393.707690575478</v>
       </c>
       <c r="E2">
-        <v>7.476082971984532</v>
+        <v>7.479657088932164</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3763,16 +3763,16 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>4901.492920513861</v>
+        <v>4656.002238295375</v>
       </c>
       <c r="C3">
-        <v>4210.933616162669</v>
+        <v>4000.725008643578</v>
       </c>
       <c r="D3">
-        <v>5692.629449686699</v>
+        <v>5418.350244910015</v>
       </c>
       <c r="E3">
-        <v>7.692904492597668</v>
+        <v>7.738962097036342</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3780,16 +3780,16 @@
         <v>0.8</v>
       </c>
       <c r="B4">
-        <v>4902.509428209002</v>
+        <v>4656.250204226273</v>
       </c>
       <c r="C4">
-        <v>4199.788081181659</v>
+        <v>3983.974082211746</v>
       </c>
       <c r="D4">
-        <v>5723.456977474235</v>
+        <v>5446.498733139968</v>
       </c>
       <c r="E4">
-        <v>7.853775967627334</v>
+        <v>7.927498636592078</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -630,40 +630,40 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>4629.139016586378</v>
+        <v>4713.367605953854</v>
       </c>
       <c r="E2">
-        <v>4651.355208234036</v>
+        <v>4735.853937074027</v>
       </c>
       <c r="F2">
-        <v>4668.529798229674</v>
+        <v>4753.023930077136</v>
       </c>
       <c r="G2">
-        <v>369.8529166826939</v>
+        <v>376.0888159378201</v>
       </c>
       <c r="H2">
-        <v>7.922256741789324</v>
+        <v>7.912621974358891</v>
       </c>
       <c r="I2">
-        <v>3990.989096395166</v>
+        <v>4063.943098911555</v>
       </c>
       <c r="J2">
-        <v>4304.432851284701</v>
+        <v>4382.837752019204</v>
       </c>
       <c r="K2">
-        <v>5032.580210046819</v>
+        <v>5123.498775659029</v>
       </c>
       <c r="L2">
-        <v>5442.389715932903</v>
+        <v>5540.021488717734</v>
       </c>
       <c r="M2">
-        <v>-14.19728406615475</v>
+        <v>-14.187744113105</v>
       </c>
       <c r="N2">
-        <v>17.00653835893984</v>
+        <v>16.9804128744002</v>
       </c>
       <c r="O2">
-        <v>0.03372019957344529</v>
+        <v>0.03451066244807589</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -865,40 +865,40 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>4629.139016586378</v>
+        <v>4713.367605953854</v>
       </c>
       <c r="E7">
-        <v>3557.805652650764</v>
+        <v>3608.029670387188</v>
       </c>
       <c r="F7">
-        <v>3593.199556803037</v>
+        <v>3644.410867200063</v>
       </c>
       <c r="G7">
-        <v>383.719582755758</v>
+        <v>391.2860918531221</v>
       </c>
       <c r="H7">
-        <v>10.679050152649</v>
+        <v>10.73660753716664</v>
       </c>
       <c r="I7">
-        <v>2940.766199459483</v>
+        <v>2980.899170589511</v>
       </c>
       <c r="J7">
-        <v>3221.110220188275</v>
+        <v>3265.33932540253</v>
       </c>
       <c r="K7">
-        <v>3962.302274814746</v>
+        <v>4021.020257260481</v>
       </c>
       <c r="L7">
-        <v>4449.461140125159</v>
+        <v>4518.157424542476</v>
       </c>
       <c r="M7">
-        <v>-17.34325911623509</v>
+        <v>-17.38152280023734</v>
       </c>
       <c r="N7">
-        <v>25.06195038534669</v>
+        <v>25.22506290968556</v>
       </c>
       <c r="O7">
-        <v>0.03620472748441337</v>
+        <v>0.03418570630824501</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1118,7 +1118,7 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>86.32184887666588</v>
+        <v>86.82375431220247</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1129,7 +1129,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>0.1068499362635191</v>
+        <v>0.1029291897156972</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1140,7 +1140,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>0.009881777646257202</v>
+        <v>0.009519176160961476</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1151,7 +1151,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.002234438596120387</v>
+        <v>0.002152448211114889</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1162,7 +1162,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>5.86062255477616</v>
+        <v>5.64557314573341</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1173,7 +1173,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>7.698562416052061</v>
+        <v>7.416071727976354</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1521,13 +1521,13 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0.00018</v>
+        <v>0.00012</v>
       </c>
       <c r="E4">
-        <v>0.54589</v>
+        <v>0.52823</v>
       </c>
       <c r="F4">
-        <v>0.05353</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1581,10 +1581,10 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>0.99982</v>
+        <v>0.99988</v>
       </c>
       <c r="E7">
-        <v>0.00018</v>
+        <v>0.00012</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1604,10 +1604,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.45393</v>
+        <v>0.47165</v>
       </c>
       <c r="F8">
-        <v>0.5460700000000001</v>
+        <v>0.52835</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.4004</v>
+        <v>0.41905</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.01932</v>
+        <v>0.02011</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2421,13 +2421,13 @@
         <v>40</v>
       </c>
       <c r="D49">
-        <v>0.41399</v>
+        <v>0.39233</v>
       </c>
       <c r="E49">
-        <v>0.16194</v>
+        <v>0.16458</v>
       </c>
       <c r="F49">
-        <v>0.15045</v>
+        <v>0.15008</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2481,13 +2481,13 @@
         <v>43</v>
       </c>
       <c r="D52">
-        <v>0.32811</v>
+        <v>0.34721</v>
       </c>
       <c r="E52">
-        <v>0.11883</v>
+        <v>0.11689</v>
       </c>
       <c r="F52">
-        <v>0.08807</v>
+        <v>0.09061</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2501,13 +2501,13 @@
         <v>44</v>
       </c>
       <c r="D53">
-        <v>0.2579</v>
+        <v>0.26046</v>
       </c>
       <c r="E53">
-        <v>0.50717</v>
+        <v>0.50318</v>
       </c>
       <c r="F53">
-        <v>0.23493</v>
+        <v>0.23636</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2524,10 +2524,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.21206</v>
+        <v>0.21535</v>
       </c>
       <c r="F54">
-        <v>0.50723</v>
+        <v>0.50284</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3305,7 +3305,7 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>4656.250204226273</v>
+        <v>4740.754834468833</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4656.250204226273</v>
+        <v>4740.754834468833</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>17</v>
       </c>
       <c r="D12">
-        <v>4656.250204226273</v>
+        <v>4740.754834468833</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>4539.579626043395</v>
+        <v>4621.907529600363</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>17</v>
       </c>
       <c r="D22">
-        <v>4539.579626043395</v>
+        <v>4621.907529600363</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>4539.579626043395</v>
+        <v>4621.907529600363</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3746,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4656.511483455182</v>
+        <v>4741.353433368069</v>
       </c>
       <c r="C2">
-        <v>4024.174273137617</v>
+        <v>4096.493530952253</v>
       </c>
       <c r="D2">
-        <v>5393.707690575478</v>
+        <v>5492.97103312192</v>
       </c>
       <c r="E2">
-        <v>7.479657088932164</v>
+        <v>7.485350890554811</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3763,16 +3763,16 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>4656.002238295375</v>
+        <v>4739.996991807391</v>
       </c>
       <c r="C3">
-        <v>4000.725008643578</v>
+        <v>4073.582342654504</v>
       </c>
       <c r="D3">
-        <v>5418.350244910015</v>
+        <v>5515.670508546701</v>
       </c>
       <c r="E3">
-        <v>7.738962097036342</v>
+        <v>7.735681898531611</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3780,16 +3780,16 @@
         <v>0.8</v>
       </c>
       <c r="B4">
-        <v>4656.250204226273</v>
+        <v>4740.754834468833</v>
       </c>
       <c r="C4">
-        <v>3983.974082211746</v>
+        <v>4057.201505032894</v>
       </c>
       <c r="D4">
-        <v>5446.498733139968</v>
+        <v>5545.702306261544</v>
       </c>
       <c r="E4">
-        <v>7.927498636592078</v>
+        <v>7.91774161569511</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -12,14 +12,15 @@
     <sheet name="ranking_probabilities" sheetId="3" r:id="rId3"/>
     <sheet name="structural_scenarios" sheetId="4" r:id="rId4"/>
     <sheet name="travel_correlation" sheetId="5" r:id="rId5"/>
-    <sheet name="parameters" sheetId="6" r:id="rId6"/>
+    <sheet name="mrio_correlation" sheetId="6" r:id="rId6"/>
+    <sheet name="parameters" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="78">
   <si>
     <t>pharma_scenario</t>
   </si>
@@ -184,6 +185,21 @@
   </si>
   <si>
     <t>rho</t>
+  </si>
+  <si>
+    <t>rho_mrio</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>perfect correlation (study default, upper bound)</t>
+  </si>
+  <si>
+    <t>Rodrigues et al. 2018 measured median for country consumption-based accounts</t>
+  </si>
+  <si>
+    <t>independence (lower bound; Rodrigues et al. show this understates uncertainty)</t>
   </si>
   <si>
     <t>distribution</t>
@@ -868,37 +884,37 @@
         <v>4713.367605953854</v>
       </c>
       <c r="E7">
-        <v>3608.029670387188</v>
+        <v>3607.550496222587</v>
       </c>
       <c r="F7">
-        <v>3644.410867200063</v>
+        <v>3643.024709283456</v>
       </c>
       <c r="G7">
-        <v>391.2860918531221</v>
+        <v>390.8290630058905</v>
       </c>
       <c r="H7">
-        <v>10.73660753716664</v>
+        <v>10.7281474652079</v>
       </c>
       <c r="I7">
-        <v>2980.899170589511</v>
+        <v>2975.553880778193</v>
       </c>
       <c r="J7">
-        <v>3265.33932540253</v>
+        <v>3264.389952257232</v>
       </c>
       <c r="K7">
-        <v>4021.020257260481</v>
+        <v>4023.582675250479</v>
       </c>
       <c r="L7">
-        <v>4518.157424542476</v>
+        <v>4510.832446157484</v>
       </c>
       <c r="M7">
-        <v>-17.38152280023734</v>
+        <v>-17.51871847964841</v>
       </c>
       <c r="N7">
-        <v>25.22506290968556</v>
+        <v>25.03865021101466</v>
       </c>
       <c r="O7">
-        <v>0.03418570630824501</v>
+        <v>0.03316025501669896</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -915,37 +931,37 @@
         <v>4261.281022540152</v>
       </c>
       <c r="E8">
-        <v>2397.939093358254</v>
+        <v>2395.834001830341</v>
       </c>
       <c r="F8">
-        <v>2417.958614580572</v>
+        <v>2417.028662410227</v>
       </c>
       <c r="G8">
-        <v>246.6248454324626</v>
+        <v>247.5158807107511</v>
       </c>
       <c r="H8">
-        <v>10.19971325999072</v>
+        <v>10.24050250458891</v>
       </c>
       <c r="I8">
-        <v>1991.618823758696</v>
+        <v>1988.982415849055</v>
       </c>
       <c r="J8">
-        <v>2178.966115341834</v>
+        <v>2178.529412966601</v>
       </c>
       <c r="K8">
-        <v>2655.505501467193</v>
+        <v>2656.057408057869</v>
       </c>
       <c r="L8">
-        <v>2958.63092262199</v>
+        <v>2956.259691260682</v>
       </c>
       <c r="M8">
-        <v>-16.94456171655786</v>
+        <v>-16.98162667657543</v>
       </c>
       <c r="N8">
-        <v>23.38223814010643</v>
+        <v>23.39167442327781</v>
       </c>
       <c r="O8">
-        <v>0.04649620794505965</v>
+        <v>0.05577951146768704</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -962,37 +978,37 @@
         <v>95.51845307556377</v>
       </c>
       <c r="E9">
-        <v>70.88990789404747</v>
+        <v>70.99488542672307</v>
       </c>
       <c r="F9">
-        <v>71.42288401169881</v>
+        <v>71.48385028032602</v>
       </c>
       <c r="G9">
-        <v>15.38647510284305</v>
+        <v>15.3678650255859</v>
       </c>
       <c r="H9">
-        <v>21.54278046280349</v>
+        <v>21.49837336030496</v>
       </c>
       <c r="I9">
-        <v>45.93243271448221</v>
+        <v>45.98972737297568</v>
       </c>
       <c r="J9">
-        <v>54.37214198274688</v>
+        <v>54.40351303810704</v>
       </c>
       <c r="K9">
-        <v>88.25993698408881</v>
+        <v>88.21833878845057</v>
       </c>
       <c r="L9">
-        <v>100.6241641490363</v>
+        <v>100.8034028384659</v>
       </c>
       <c r="M9">
-        <v>-35.20596361454844</v>
+        <v>-35.22106966361163</v>
       </c>
       <c r="N9">
-        <v>41.9442726592759</v>
+        <v>41.98685191556446</v>
       </c>
       <c r="O9">
-        <v>0.1081542795426334</v>
+        <v>0.09826821536790505</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1009,37 +1025,37 @@
         <v>4855.583327817173</v>
       </c>
       <c r="E10">
-        <v>3961.772006685232</v>
+        <v>3966.50968158735</v>
       </c>
       <c r="F10">
-        <v>3990.071165559074</v>
+        <v>3990.602873859455</v>
       </c>
       <c r="G10">
-        <v>610.6449435575681</v>
+        <v>608.5723637520845</v>
       </c>
       <c r="H10">
-        <v>15.30411158649114</v>
+        <v>15.2501359566133</v>
       </c>
       <c r="I10">
-        <v>2939.171068356145</v>
+        <v>2945.72192218013</v>
       </c>
       <c r="J10">
-        <v>3342.091747790692</v>
+        <v>3343.585375425527</v>
       </c>
       <c r="K10">
-        <v>4633.532435036369</v>
+        <v>4628.213908707865</v>
       </c>
       <c r="L10">
-        <v>5211.684516676283</v>
+        <v>5208.914692158903</v>
       </c>
       <c r="M10">
-        <v>-25.81170588826197</v>
+        <v>-25.73516369179043</v>
       </c>
       <c r="N10">
-        <v>31.54932964042114</v>
+        <v>31.32237433678358</v>
       </c>
       <c r="O10">
-        <v>0.07160027093183655</v>
+        <v>0.08654395230976082</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1056,37 +1072,37 @@
         <v>259.4180916719396</v>
       </c>
       <c r="E11">
-        <v>216.1736775271942</v>
+        <v>216.3333926896765</v>
       </c>
       <c r="F11">
-        <v>217.3822134490496</v>
+        <v>217.4884476366681</v>
       </c>
       <c r="G11">
-        <v>29.0786386413359</v>
+        <v>29.17034517859893</v>
       </c>
       <c r="H11">
-        <v>13.37673316503946</v>
+        <v>13.41236534426432</v>
       </c>
       <c r="I11">
-        <v>167.4231525537851</v>
+        <v>167.2198895987555</v>
       </c>
       <c r="J11">
-        <v>186.4274030481546</v>
+        <v>186.3742805490548</v>
       </c>
       <c r="K11">
-        <v>248.2257348088353</v>
+        <v>248.3732595722919</v>
       </c>
       <c r="L11">
-        <v>275.0192199817689</v>
+        <v>274.9911097209454</v>
       </c>
       <c r="M11">
-        <v>-22.55155462545912</v>
+        <v>-22.70269165582438</v>
       </c>
       <c r="N11">
-        <v>27.221418966318</v>
+        <v>27.11449966275508</v>
       </c>
       <c r="O11">
-        <v>0.07939984160304175</v>
+        <v>0.05574829518999678</v>
       </c>
     </row>
   </sheetData>
@@ -2387,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.02011</v>
+        <v>0.02062</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2421,13 +2437,13 @@
         <v>40</v>
       </c>
       <c r="D49">
-        <v>0.39233</v>
+        <v>0.39285</v>
       </c>
       <c r="E49">
-        <v>0.16458</v>
+        <v>0.16322</v>
       </c>
       <c r="F49">
-        <v>0.15008</v>
+        <v>0.15168</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2481,13 +2497,13 @@
         <v>43</v>
       </c>
       <c r="D52">
-        <v>0.34721</v>
+        <v>0.3454</v>
       </c>
       <c r="E52">
-        <v>0.11689</v>
+        <v>0.11654</v>
       </c>
       <c r="F52">
-        <v>0.09061</v>
+        <v>0.09107</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2501,13 +2517,13 @@
         <v>44</v>
       </c>
       <c r="D53">
-        <v>0.26046</v>
+        <v>0.26175</v>
       </c>
       <c r="E53">
-        <v>0.50318</v>
+        <v>0.50288</v>
       </c>
       <c r="F53">
-        <v>0.23636</v>
+        <v>0.23537</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2524,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.21535</v>
+        <v>0.21736</v>
       </c>
       <c r="F54">
-        <v>0.50284</v>
+        <v>0.50126</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2627,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0.07764</v>
+        <v>0.07897999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2661,13 +2677,13 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.00057</v>
+        <v>0.00056</v>
       </c>
       <c r="E61">
-        <v>0.35161</v>
+        <v>0.34987</v>
       </c>
       <c r="F61">
-        <v>0.57018</v>
+        <v>0.57059</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2684,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.64782</v>
+        <v>0.64957</v>
       </c>
       <c r="F62">
-        <v>0.35218</v>
+        <v>0.35043</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2721,10 +2737,10 @@
         <v>46</v>
       </c>
       <c r="D64">
-        <v>0.99943</v>
+        <v>0.99944</v>
       </c>
       <c r="E64">
-        <v>0.00057</v>
+        <v>0.00056</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2741,10 +2757,10 @@
         <v>38</v>
       </c>
       <c r="D65">
-        <v>0.24605</v>
+        <v>0.2459</v>
       </c>
       <c r="E65">
-        <v>0.75395</v>
+        <v>0.7541</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2841,13 +2857,13 @@
         <v>43</v>
       </c>
       <c r="D70">
-        <v>0.75395</v>
+        <v>0.7541</v>
       </c>
       <c r="E70">
-        <v>0.19277</v>
+        <v>0.19259</v>
       </c>
       <c r="F70">
-        <v>0.05328</v>
+        <v>0.05331</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2864,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.05328</v>
+        <v>0.05331</v>
       </c>
       <c r="F71">
-        <v>0.94672</v>
+        <v>0.94669</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2921,10 +2937,10 @@
         <v>38</v>
       </c>
       <c r="D74">
-        <v>0.73704</v>
+        <v>0.73628</v>
       </c>
       <c r="E74">
-        <v>0.26296</v>
+        <v>0.26372</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3021,13 +3037,13 @@
         <v>43</v>
       </c>
       <c r="D79">
-        <v>0.26296</v>
+        <v>0.26372</v>
       </c>
       <c r="E79">
-        <v>0.50726</v>
+        <v>0.50845</v>
       </c>
       <c r="F79">
-        <v>0.22978</v>
+        <v>0.22783</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3044,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0.22978</v>
+        <v>0.22783</v>
       </c>
       <c r="F80">
-        <v>0.77022</v>
+        <v>0.77217</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3104,10 +3120,10 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0.0072</v>
+        <v>0.00756</v>
       </c>
       <c r="F83">
-        <v>0.24611</v>
+        <v>0.2461</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3181,13 +3197,13 @@
         <v>42</v>
       </c>
       <c r="D87">
-        <v>0.31542</v>
+        <v>0.3145</v>
       </c>
       <c r="E87">
-        <v>0.61151</v>
+        <v>0.6122300000000001</v>
       </c>
       <c r="F87">
-        <v>0.04639</v>
+        <v>0.04669</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3201,13 +3217,13 @@
         <v>43</v>
       </c>
       <c r="D88">
-        <v>0.66331</v>
+        <v>0.6639</v>
       </c>
       <c r="E88">
-        <v>0.08656999999999999</v>
+        <v>0.08562</v>
       </c>
       <c r="F88">
-        <v>0.02326</v>
+        <v>0.02306</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3227,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0.00023</v>
+        <v>0.00034</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3261,13 +3277,13 @@
         <v>46</v>
       </c>
       <c r="D91">
-        <v>0.02127</v>
+        <v>0.0216</v>
       </c>
       <c r="E91">
-        <v>0.29472</v>
+        <v>0.29459</v>
       </c>
       <c r="F91">
-        <v>0.68401</v>
+        <v>0.68381</v>
       </c>
     </row>
   </sheetData>
@@ -3799,6 +3815,96 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2">
+        <v>4740.754834468833</v>
+      </c>
+      <c r="D2">
+        <v>4057.201505032894</v>
+      </c>
+      <c r="E2">
+        <v>5545.702306261544</v>
+      </c>
+      <c r="F2">
+        <v>7.91774161569511</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>0.76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3">
+        <v>4739.376149412801</v>
+      </c>
+      <c r="D3">
+        <v>4114.297537506432</v>
+      </c>
+      <c r="E3">
+        <v>5476.614809800862</v>
+      </c>
+      <c r="F3">
+        <v>7.338779835986881</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <v>4737.923134306791</v>
+      </c>
+      <c r="D4">
+        <v>4314.697258683934</v>
+      </c>
+      <c r="E4">
+        <v>5273.513454289891</v>
+      </c>
+      <c r="F4">
+        <v>5.152459723363281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -3807,22 +3913,22 @@
         <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3830,7 +3936,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D2">
         <v>0.0835</v>
@@ -3842,15 +3948,15 @@
         <v>1.177479106404468</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>1.1</v>
@@ -3862,15 +3968,15 @@
         <v>1.205395769474916</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>1.3</v>
@@ -3882,15 +3988,15 @@
         <v>1.672356915945362</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>1.15</v>
@@ -3902,15 +4008,15 @@
         <v>1.315127221128319</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>1.25</v>
@@ -3922,15 +4028,15 @@
         <v>1.548615584577687</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>1.4</v>
@@ -3942,7 +4048,7 @@
         <v>1.933797301790597</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -693,40 +693,40 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>4261.281022540152</v>
+        <v>4259.384222540152</v>
       </c>
       <c r="E3">
-        <v>4259.162191257918</v>
+        <v>4257.15069438269</v>
       </c>
       <c r="F3">
-        <v>4275.801191769181</v>
+        <v>4273.794871725224</v>
       </c>
       <c r="G3">
-        <v>356.1667648625975</v>
+        <v>356.153175792993</v>
       </c>
       <c r="H3">
-        <v>8.32982519271968</v>
+        <v>8.333417641292243</v>
       </c>
       <c r="I3">
-        <v>3621.269076316772</v>
+        <v>3619.030837206768</v>
       </c>
       <c r="J3">
-        <v>3924.37894030944</v>
+        <v>3922.193288124661</v>
       </c>
       <c r="K3">
-        <v>4628.31077990047</v>
+        <v>4626.263055507859</v>
       </c>
       <c r="L3">
-        <v>5017.491585606876</v>
+        <v>5015.423903738685</v>
       </c>
       <c r="M3">
-        <v>-14.97696228263963</v>
+        <v>-14.98936502336928</v>
       </c>
       <c r="N3">
-        <v>17.80466111164905</v>
+        <v>17.81175400618391</v>
       </c>
       <c r="O3">
-        <v>0.04250637541064802</v>
+        <v>0.04237824796965083</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -740,40 +740,40 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>95.51845307556377</v>
+        <v>95.50495307556376</v>
       </c>
       <c r="E4">
-        <v>95.45468832677814</v>
+        <v>95.43851311641362</v>
       </c>
       <c r="F4">
-        <v>95.82719494375063</v>
+        <v>95.81291546220623</v>
       </c>
       <c r="G4">
-        <v>8.017561729515547</v>
+        <v>8.017532601500815</v>
       </c>
       <c r="H4">
-        <v>8.366687279348787</v>
+        <v>8.367903807982296</v>
       </c>
       <c r="I4">
-        <v>81.10242947302176</v>
+        <v>81.08922953860821</v>
       </c>
       <c r="J4">
-        <v>87.91022568826547</v>
+        <v>87.89489792963221</v>
       </c>
       <c r="K4">
-        <v>103.7533883649353</v>
+        <v>103.7394689599238</v>
       </c>
       <c r="L4">
-        <v>112.5260073444621</v>
+        <v>112.5143563600497</v>
       </c>
       <c r="M4">
-        <v>-15.03567724680329</v>
+        <v>-15.03510805989034</v>
       </c>
       <c r="N4">
-        <v>17.8842122025922</v>
+        <v>17.89198373491774</v>
       </c>
       <c r="O4">
-        <v>0.04252884922528793</v>
+        <v>0.0423092331390826</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -787,40 +787,40 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>4855.583327817173</v>
+        <v>4855.460127817173</v>
       </c>
       <c r="E5">
-        <v>4851.906633386088</v>
+        <v>4851.791433545872</v>
       </c>
       <c r="F5">
-        <v>4870.961891764669</v>
+        <v>4870.831578273835</v>
       </c>
       <c r="G5">
-        <v>408.2190442544017</v>
+        <v>408.2190058041871</v>
       </c>
       <c r="H5">
-        <v>8.380665940839679</v>
+        <v>8.380889366510495</v>
       </c>
       <c r="I5">
-        <v>4121.369138332022</v>
+        <v>4121.255246781522</v>
       </c>
       <c r="J5">
-        <v>4467.788669920978</v>
+        <v>4467.667891523526</v>
       </c>
       <c r="K5">
-        <v>5274.424314824582</v>
+        <v>5274.311827882727</v>
       </c>
       <c r="L5">
-        <v>5721.682126200532</v>
+        <v>5721.563292112829</v>
       </c>
       <c r="M5">
-        <v>-15.05670966599439</v>
+        <v>-15.05704020402307</v>
       </c>
       <c r="N5">
-        <v>17.92646805751574</v>
+        <v>17.92681879425504</v>
       </c>
       <c r="O5">
-        <v>0.04195994547778891</v>
+        <v>0.04194725003660093</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -928,40 +928,40 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>4261.281022540152</v>
+        <v>4259.384222540152</v>
       </c>
       <c r="E8">
-        <v>2395.834001830341</v>
+        <v>2393.808065435534</v>
       </c>
       <c r="F8">
-        <v>2417.028662410227</v>
+        <v>2415.02234236627</v>
       </c>
       <c r="G8">
-        <v>247.5158807107511</v>
+        <v>247.4974208234635</v>
       </c>
       <c r="H8">
-        <v>10.24050250458891</v>
+        <v>10.24824559515099</v>
       </c>
       <c r="I8">
-        <v>1988.982415849055</v>
+        <v>1987.431079443819</v>
       </c>
       <c r="J8">
-        <v>2178.529412966601</v>
+        <v>2176.514010645478</v>
       </c>
       <c r="K8">
-        <v>2656.057408057869</v>
+        <v>2653.956656035499</v>
       </c>
       <c r="L8">
-        <v>2956.259691260682</v>
+        <v>2953.955916931678</v>
       </c>
       <c r="M8">
-        <v>-16.98162667657543</v>
+        <v>-16.97617247846381</v>
       </c>
       <c r="N8">
-        <v>23.39167442327781</v>
+        <v>23.39986482559662</v>
       </c>
       <c r="O8">
-        <v>0.05577951146768704</v>
+        <v>0.05620695431357499</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="D9">
-        <v>95.51845307556377</v>
+        <v>95.50495307556376</v>
       </c>
       <c r="E9">
-        <v>70.99488542672307</v>
+        <v>70.97917317385307</v>
       </c>
       <c r="F9">
-        <v>71.48385028032602</v>
+        <v>71.46957079878163</v>
       </c>
       <c r="G9">
-        <v>15.3678650255859</v>
+        <v>15.36785178753142</v>
       </c>
       <c r="H9">
-        <v>21.49837336030496</v>
+        <v>21.50265017093596</v>
       </c>
       <c r="I9">
-        <v>45.98972737297568</v>
+        <v>45.97630555679345</v>
       </c>
       <c r="J9">
-        <v>54.40351303810704</v>
+        <v>54.39043857046833</v>
       </c>
       <c r="K9">
-        <v>88.21833878845057</v>
+        <v>88.20393365030614</v>
       </c>
       <c r="L9">
-        <v>100.8034028384659</v>
+        <v>100.7898787437053</v>
       </c>
       <c r="M9">
-        <v>-35.22106966361163</v>
+        <v>-35.22563943625937</v>
       </c>
       <c r="N9">
-        <v>41.98685191556446</v>
+        <v>41.99922912152729</v>
       </c>
       <c r="O9">
-        <v>0.09826821536790505</v>
+        <v>0.09793570371006248</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1022,40 +1022,40 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>4855.583327817173</v>
+        <v>4855.460127817173</v>
       </c>
       <c r="E10">
-        <v>3966.50968158735</v>
+        <v>3966.39043352187</v>
       </c>
       <c r="F10">
-        <v>3990.602873859455</v>
+        <v>3990.472560368619</v>
       </c>
       <c r="G10">
-        <v>608.5723637520845</v>
+        <v>608.5723168512517</v>
       </c>
       <c r="H10">
-        <v>15.2501359566133</v>
+        <v>15.25063279209806</v>
       </c>
       <c r="I10">
-        <v>2945.72192218013</v>
+        <v>2945.502333820155</v>
       </c>
       <c r="J10">
-        <v>3343.585375425527</v>
+        <v>3343.478035167852</v>
       </c>
       <c r="K10">
-        <v>4628.213908707865</v>
+        <v>4628.052201938835</v>
       </c>
       <c r="L10">
-        <v>5208.914692158903</v>
+        <v>5208.779771112454</v>
       </c>
       <c r="M10">
-        <v>-25.73516369179043</v>
+        <v>-25.73846717342043</v>
       </c>
       <c r="N10">
-        <v>31.32237433678358</v>
+        <v>31.32292088773094</v>
       </c>
       <c r="O10">
-        <v>0.08654395230976082</v>
+        <v>0.08647818737329281</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1200,7 +1200,7 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>99.97363589809672</v>
+        <v>99.97832825764083</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1244,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0.00956856446188631</v>
+        <v>0.009569013571737851</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1255,7 +1255,7 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>0.01679553744138497</v>
+        <v>0.01210272878743249</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1266,7 +1266,7 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>99.99744441935184</v>
+        <v>99.99791506389099</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1310,7 +1310,7 @@
         <v>32</v>
       </c>
       <c r="C18">
-        <v>0.0008664555258324851</v>
+        <v>0.0008664596038623189</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="C19">
-        <v>0.001689125122333169</v>
+        <v>0.001218476505164445</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1332,7 +1332,7 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>99.99991506020071</v>
+        <v>99.99993013811309</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1376,7 +1376,7 @@
         <v>32</v>
       </c>
       <c r="C24">
-        <v>3.095345705543773E-05</v>
+        <v>3.095346172257683E-05</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1387,7 +1387,7 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>5.398634223171339E-05</v>
+        <v>3.890842518563305E-05</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3335,7 +3335,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>4262.552479823979</v>
+        <v>4260.737987822766</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>95.51884731880483</v>
+        <v>95.50059516486002</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>4854.862058366974</v>
+        <v>4854.731019167153</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>4262.552479823979</v>
+        <v>4260.737987822766</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>95.51884731880483</v>
+        <v>95.50059516486002</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>20</v>
       </c>
       <c r="D10">
-        <v>4854.862058366974</v>
+        <v>4854.731019167153</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>18</v>
       </c>
       <c r="D13">
-        <v>4262.552479823979</v>
+        <v>4260.737987822766</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3489,7 +3489,7 @@
         <v>19</v>
       </c>
       <c r="D14">
-        <v>95.51884731880483</v>
+        <v>95.50059516486002</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3503,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="D15">
-        <v>4854.862058366974</v>
+        <v>4854.731019167153</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>18</v>
       </c>
       <c r="D18">
-        <v>4135.47464587318</v>
+        <v>4133.549380028947</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>92.65953114599043</v>
+        <v>92.64229592541933</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>4709.269371156532</v>
+        <v>4709.138331956709</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>18</v>
       </c>
       <c r="D23">
-        <v>4135.47464587318</v>
+        <v>4133.549380028947</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>92.65953114599043</v>
+        <v>92.64229592541933</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>20</v>
       </c>
       <c r="D25">
-        <v>4709.269371156532</v>
+        <v>4709.138331956709</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>18</v>
       </c>
       <c r="D28">
-        <v>4135.47464587318</v>
+        <v>4133.549380028947</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>92.65953114599043</v>
+        <v>92.64229592541933</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>20</v>
       </c>
       <c r="D30">
-        <v>4709.269371156532</v>
+        <v>4709.138331956709</v>
       </c>
     </row>
     <row r="31" spans="1:4">

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="79">
   <si>
     <t>pharma_scenario</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>B_VISI</t>
+  </si>
+  <si>
+    <t>covariance_commute_visitor</t>
   </si>
   <si>
     <t>group</t>
@@ -649,37 +652,37 @@
         <v>4713.367605953854</v>
       </c>
       <c r="E2">
-        <v>4735.853937074027</v>
+        <v>4734.725238865476</v>
       </c>
       <c r="F2">
-        <v>4753.023930077136</v>
+        <v>4750.935562516105</v>
       </c>
       <c r="G2">
-        <v>376.0888159378201</v>
+        <v>373.7878496002326</v>
       </c>
       <c r="H2">
-        <v>7.912621974358891</v>
+        <v>7.867668266211418</v>
       </c>
       <c r="I2">
-        <v>4063.943098911555</v>
+        <v>4064.511469512162</v>
       </c>
       <c r="J2">
-        <v>4382.837752019204</v>
+        <v>4382.869614413962</v>
       </c>
       <c r="K2">
-        <v>5123.498775659029</v>
+        <v>5119.360556791389</v>
       </c>
       <c r="L2">
-        <v>5540.021488717734</v>
+        <v>5532.19898998981</v>
       </c>
       <c r="M2">
-        <v>-14.187744113105</v>
+        <v>-14.15528326441829</v>
       </c>
       <c r="N2">
-        <v>16.9804128744002</v>
+        <v>16.8430840416713</v>
       </c>
       <c r="O2">
-        <v>0.03451066244807589</v>
+        <v>0.03587953771436504</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -696,37 +699,37 @@
         <v>4259.384222540152</v>
       </c>
       <c r="E3">
-        <v>4257.15069438269</v>
+        <v>4257.064040750247</v>
       </c>
       <c r="F3">
-        <v>4273.794871725224</v>
+        <v>4273.708866669909</v>
       </c>
       <c r="G3">
-        <v>356.153175792993</v>
+        <v>356.1502975439804</v>
       </c>
       <c r="H3">
-        <v>8.333417641292243</v>
+        <v>8.333517997015415</v>
       </c>
       <c r="I3">
-        <v>3619.030837206768</v>
+        <v>3619.18783340865</v>
       </c>
       <c r="J3">
-        <v>3922.193288124661</v>
+        <v>3922.235659339767</v>
       </c>
       <c r="K3">
-        <v>4626.263055507859</v>
+        <v>4626.026447384603</v>
       </c>
       <c r="L3">
-        <v>5015.423903738685</v>
+        <v>5015.634895065245</v>
       </c>
       <c r="M3">
-        <v>-14.98936502336928</v>
+        <v>-14.98394671152704</v>
       </c>
       <c r="N3">
-        <v>17.81175400618391</v>
+        <v>17.81910835856986</v>
       </c>
       <c r="O3">
-        <v>0.04237824796965083</v>
+        <v>0.04272565801579455</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -743,37 +746,37 @@
         <v>95.50495307556376</v>
       </c>
       <c r="E4">
-        <v>95.43851311641362</v>
+        <v>95.43813629775974</v>
       </c>
       <c r="F4">
-        <v>95.81291546220623</v>
+        <v>95.81233248421557</v>
       </c>
       <c r="G4">
-        <v>8.017532601500815</v>
+        <v>8.017534974300801</v>
       </c>
       <c r="H4">
-        <v>8.367903807982296</v>
+        <v>8.367957199686831</v>
       </c>
       <c r="I4">
-        <v>81.08922953860821</v>
+        <v>81.09304581706947</v>
       </c>
       <c r="J4">
-        <v>87.89489792963221</v>
+        <v>87.89496439031208</v>
       </c>
       <c r="K4">
-        <v>103.7394689599238</v>
+        <v>103.7378614710755</v>
       </c>
       <c r="L4">
-        <v>112.5143563600497</v>
+        <v>112.5168035974762</v>
       </c>
       <c r="M4">
-        <v>-15.03510805989034</v>
+        <v>-15.03077389937151</v>
       </c>
       <c r="N4">
-        <v>17.89198373491774</v>
+        <v>17.89501342150304</v>
       </c>
       <c r="O4">
-        <v>0.0423092331390826</v>
+        <v>0.04245873157448145</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -790,37 +793,37 @@
         <v>4855.460127817173</v>
       </c>
       <c r="E5">
-        <v>4851.791433545872</v>
+        <v>4851.806936702707</v>
       </c>
       <c r="F5">
-        <v>4870.831578273835</v>
+        <v>4870.825971144449</v>
       </c>
       <c r="G5">
-        <v>408.2190058041871</v>
+        <v>408.2190717515793</v>
       </c>
       <c r="H5">
-        <v>8.380889366510495</v>
+        <v>8.380900368231883</v>
       </c>
       <c r="I5">
-        <v>4121.255246781522</v>
+        <v>4121.277132756415</v>
       </c>
       <c r="J5">
-        <v>4467.667891523526</v>
+        <v>4467.611407018141</v>
       </c>
       <c r="K5">
-        <v>5274.311827882727</v>
+        <v>5274.302890348879</v>
       </c>
       <c r="L5">
-        <v>5721.563292112829</v>
+        <v>5721.499313286949</v>
       </c>
       <c r="M5">
-        <v>-15.05704020402307</v>
+        <v>-15.05686053622656</v>
       </c>
       <c r="N5">
-        <v>17.92681879425504</v>
+        <v>17.92512331859777</v>
       </c>
       <c r="O5">
-        <v>0.04194725003660093</v>
+        <v>0.04202104937659471</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -884,37 +887,37 @@
         <v>4713.367605953854</v>
       </c>
       <c r="E7">
-        <v>3607.550496222587</v>
+        <v>3605.390020206104</v>
       </c>
       <c r="F7">
-        <v>3643.024709283456</v>
+        <v>3640.936341722425</v>
       </c>
       <c r="G7">
-        <v>390.8290630058905</v>
+        <v>388.6479453529622</v>
       </c>
       <c r="H7">
-        <v>10.7281474652079</v>
+        <v>10.67439550918113</v>
       </c>
       <c r="I7">
-        <v>2975.553880778193</v>
+        <v>2980.086319286984</v>
       </c>
       <c r="J7">
-        <v>3264.389952257232</v>
+        <v>3263.73190929662</v>
       </c>
       <c r="K7">
-        <v>4023.582675250479</v>
+        <v>4020.695496597223</v>
       </c>
       <c r="L7">
-        <v>4510.832446157484</v>
+        <v>4502.750577485003</v>
       </c>
       <c r="M7">
-        <v>-17.51871847964841</v>
+        <v>-17.34357995708253</v>
       </c>
       <c r="N7">
-        <v>25.03865021101466</v>
+        <v>24.88941701867808</v>
       </c>
       <c r="O7">
-        <v>0.03316025501669896</v>
+        <v>0.0313307960326539</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -931,37 +934,37 @@
         <v>4259.384222540152</v>
       </c>
       <c r="E8">
-        <v>2393.808065435534</v>
+        <v>2393.748478938714</v>
       </c>
       <c r="F8">
-        <v>2415.02234236627</v>
+        <v>2414.936337310955</v>
       </c>
       <c r="G8">
-        <v>247.4974208234635</v>
+        <v>247.4925726876774</v>
       </c>
       <c r="H8">
-        <v>10.24824559515099</v>
+        <v>10.2484098178448</v>
       </c>
       <c r="I8">
-        <v>1987.431079443819</v>
+        <v>1987.39825231248</v>
       </c>
       <c r="J8">
-        <v>2176.514010645478</v>
+        <v>2176.325512673546</v>
       </c>
       <c r="K8">
-        <v>2653.956656035499</v>
+        <v>2653.893697847422</v>
       </c>
       <c r="L8">
-        <v>2953.955916931678</v>
+        <v>2954.056371768522</v>
       </c>
       <c r="M8">
-        <v>-16.97617247846381</v>
+        <v>-16.97547717320712</v>
       </c>
       <c r="N8">
-        <v>23.39986482559662</v>
+        <v>23.40713311192262</v>
       </c>
       <c r="O8">
-        <v>0.05620695431357499</v>
+        <v>0.05582481553875492</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -978,37 +981,37 @@
         <v>95.50495307556376</v>
       </c>
       <c r="E9">
-        <v>70.97917317385307</v>
+        <v>70.9779644847637</v>
       </c>
       <c r="F9">
-        <v>71.46957079878163</v>
+        <v>71.46898782079096</v>
       </c>
       <c r="G9">
-        <v>15.36785178753142</v>
+        <v>15.36784329407484</v>
       </c>
       <c r="H9">
-        <v>21.50265017093596</v>
+        <v>21.50281368558042</v>
       </c>
       <c r="I9">
-        <v>45.97630555679345</v>
+        <v>45.97856629851675</v>
       </c>
       <c r="J9">
-        <v>54.39043857046833</v>
+        <v>54.38937292011902</v>
       </c>
       <c r="K9">
-        <v>88.20393365030614</v>
+        <v>88.20293555976561</v>
       </c>
       <c r="L9">
-        <v>100.7898787437053</v>
+        <v>100.7961201871926</v>
       </c>
       <c r="M9">
-        <v>-35.22563943625937</v>
+        <v>-35.22135125699945</v>
       </c>
       <c r="N9">
-        <v>41.99922912152729</v>
+        <v>42.01044073168616</v>
       </c>
       <c r="O9">
-        <v>0.09793570371006248</v>
+        <v>0.09775313726266661</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1025,37 +1028,37 @@
         <v>4855.460127817173</v>
       </c>
       <c r="E10">
-        <v>3966.39043352187</v>
+        <v>3966.317150993645</v>
       </c>
       <c r="F10">
-        <v>3990.472560368619</v>
+        <v>3990.466953239234</v>
       </c>
       <c r="G10">
-        <v>608.5723168512517</v>
+        <v>608.5719604512628</v>
       </c>
       <c r="H10">
-        <v>15.25063279209806</v>
+        <v>15.25064528995181</v>
       </c>
       <c r="I10">
-        <v>2945.502333820155</v>
+        <v>2945.500175850812</v>
       </c>
       <c r="J10">
-        <v>3343.478035167852</v>
+        <v>3343.401580152713</v>
       </c>
       <c r="K10">
-        <v>4628.052201938835</v>
+        <v>4628.117920975161</v>
       </c>
       <c r="L10">
-        <v>5208.779771112454</v>
+        <v>5208.729260629635</v>
       </c>
       <c r="M10">
-        <v>-25.73846717342043</v>
+        <v>-25.73714950876021</v>
       </c>
       <c r="N10">
-        <v>31.32292088773094</v>
+        <v>31.32407375251724</v>
       </c>
       <c r="O10">
-        <v>0.08647818737329281</v>
+        <v>0.0863540884311406</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1112,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1134,7 +1137,7 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>86.82375431220247</v>
+        <v>78.75829747123008</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1145,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>0.1029291897156972</v>
+        <v>0.09336762509660612</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1156,7 +1159,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>0.009519176160961476</v>
+        <v>0.008634896218265452</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1167,7 +1170,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.002152448211114889</v>
+        <v>0.001952497422454561</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1178,7 +1181,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>5.64557314573341</v>
+        <v>5.121129957228417</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1189,18 +1192,18 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>7.416071727976354</v>
+        <v>6.727158804026204</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>99.97832825764083</v>
+        <v>9.289458748777989</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1208,10 +1211,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>99.96130279917118</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1219,7 +1222,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1230,7 +1233,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1241,10 +1244,10 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>0.009569013571737851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1252,32 +1255,32 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>0.01210272878743249</v>
+        <v>0.009567384050160522</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>99.99791506389099</v>
+        <v>0.01210066779571628</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.01702914898293667</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1285,10 +1288,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>99.99628892253683</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1296,7 +1299,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1307,10 +1310,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18">
-        <v>0.0008664596038623189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1318,43 +1321,43 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19">
-        <v>0.001218476505164445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C20">
-        <v>99.99993013811309</v>
+        <v>0.0008664455137106128</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.001218456690600983</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.001626175258872878</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1362,10 +1365,10 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>99.99987521342874</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1373,10 +1376,10 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>3.095346172257683E-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1384,54 +1387,54 @@
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C25">
-        <v>3.890842518563305E-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>95.14012854415468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>4.859871455845328</v>
+        <v>3.095344472147381E-05</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>3.890840381528841E-05</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>5.492472271967433E-05</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1439,10 +1442,10 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>95.14012854415468</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1450,9 +1453,64 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31">
+        <v>4.859871455845328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
         <v>33</v>
       </c>
-      <c r="C31">
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36">
         <v>0</v>
       </c>
     </row>
@@ -1474,16 +1532,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1494,7 +1552,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1514,7 +1572,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1534,16 +1592,16 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>0.00012</v>
+        <v>0.00011</v>
       </c>
       <c r="E4">
-        <v>0.52823</v>
+        <v>0.52424</v>
       </c>
       <c r="F4">
-        <v>0.0526</v>
+        <v>0.05522</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1554,7 +1612,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1574,7 +1632,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1594,13 +1652,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7">
-        <v>0.99988</v>
+        <v>0.9998899999999999</v>
       </c>
       <c r="E7">
-        <v>0.00012</v>
+        <v>0.00011</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1614,16 +1672,16 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.47165</v>
+        <v>0.47565</v>
       </c>
       <c r="F8">
-        <v>0.52835</v>
+        <v>0.52435</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1634,7 +1692,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1643,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.41905</v>
+        <v>0.42043</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1654,7 +1712,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1674,7 +1732,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1694,7 +1752,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1714,7 +1772,7 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1734,7 +1792,7 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1754,7 +1812,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1774,7 +1832,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1794,7 +1852,7 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1814,7 +1872,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1834,7 +1892,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1854,7 +1912,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1874,7 +1932,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1894,7 +1952,7 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1914,7 +1972,7 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1934,7 +1992,7 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1954,7 +2012,7 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1974,7 +2032,7 @@
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1994,7 +2052,7 @@
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2014,7 +2072,7 @@
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2034,7 +2092,7 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2054,7 +2112,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2074,7 +2132,7 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2094,7 +2152,7 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2114,7 +2172,7 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2134,7 +2192,7 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2154,7 +2212,7 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2174,7 +2232,7 @@
         <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2194,7 +2252,7 @@
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2214,7 +2272,7 @@
         <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2234,7 +2292,7 @@
         <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2254,7 +2312,7 @@
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2274,7 +2332,7 @@
         <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2294,7 +2352,7 @@
         <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2314,7 +2372,7 @@
         <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2334,7 +2392,7 @@
         <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2354,7 +2412,7 @@
         <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2374,7 +2432,7 @@
         <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2394,7 +2452,7 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2403,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0.02062</v>
+        <v>0.01932</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2414,7 +2472,7 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2434,16 +2492,16 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D49">
-        <v>0.39285</v>
+        <v>0.38823</v>
       </c>
       <c r="E49">
-        <v>0.16322</v>
+        <v>0.16574</v>
       </c>
       <c r="F49">
-        <v>0.15168</v>
+        <v>0.15578</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2454,7 +2512,7 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2474,7 +2532,7 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2494,16 +2552,16 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D52">
-        <v>0.3454</v>
+        <v>0.34721</v>
       </c>
       <c r="E52">
-        <v>0.11654</v>
+        <v>0.11467</v>
       </c>
       <c r="F52">
-        <v>0.09107</v>
+        <v>0.09002</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2514,16 +2572,16 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53">
-        <v>0.26175</v>
+        <v>0.26456</v>
       </c>
       <c r="E53">
-        <v>0.50288</v>
+        <v>0.50126</v>
       </c>
       <c r="F53">
-        <v>0.23537</v>
+        <v>0.23418</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2534,16 +2592,16 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.21736</v>
+        <v>0.21833</v>
       </c>
       <c r="F54">
-        <v>0.50126</v>
+        <v>0.5007</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2554,7 +2612,7 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2574,7 +2632,7 @@
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2594,7 +2652,7 @@
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2614,7 +2672,7 @@
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2634,7 +2692,7 @@
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2654,7 +2712,7 @@
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2674,7 +2732,7 @@
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D61">
         <v>0.00056</v>
@@ -2694,7 +2752,7 @@
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2714,7 +2772,7 @@
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2734,7 +2792,7 @@
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D64">
         <v>0.99944</v>
@@ -2754,7 +2812,7 @@
         <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D65">
         <v>0.2459</v>
@@ -2774,7 +2832,7 @@
         <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2794,7 +2852,7 @@
         <v>19</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2814,7 +2872,7 @@
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2834,7 +2892,7 @@
         <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2854,7 +2912,7 @@
         <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D70">
         <v>0.7541</v>
@@ -2874,7 +2932,7 @@
         <v>19</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2894,7 +2952,7 @@
         <v>19</v>
       </c>
       <c r="C72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2914,7 +2972,7 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2934,7 +2992,7 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D74">
         <v>0.73628</v>
@@ -2954,7 +3012,7 @@
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2974,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2994,7 +3052,7 @@
         <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3014,7 +3072,7 @@
         <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3034,7 +3092,7 @@
         <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D79">
         <v>0.26372</v>
@@ -3054,7 +3112,7 @@
         <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3074,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3094,7 +3152,7 @@
         <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3114,7 +3172,7 @@
         <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3134,7 +3192,7 @@
         <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3154,7 +3212,7 @@
         <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3174,7 +3232,7 @@
         <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3194,7 +3252,7 @@
         <v>21</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D87">
         <v>0.3145</v>
@@ -3214,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D88">
         <v>0.6639</v>
@@ -3234,7 +3292,7 @@
         <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3254,7 +3312,7 @@
         <v>21</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3274,7 +3332,7 @@
         <v>21</v>
       </c>
       <c r="C91" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D91">
         <v>0.0216</v>
@@ -3298,10 +3356,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -3312,66 +3370,66 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>4740.754834468833</v>
+        <v>4737.95107948982</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>4260.737987822766</v>
+        <v>4260.422823120769</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>95.50059516486002</v>
+        <v>95.49982787020204</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>4854.731019167153</v>
+        <v>4854.722370151818</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -3382,66 +3440,66 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4740.754834468833</v>
+        <v>4737.95107948982</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8">
-        <v>4260.737987822766</v>
+        <v>4260.422823120769</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9">
-        <v>95.50059516486002</v>
+        <v>95.49982787020204</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10">
-        <v>4854.731019167153</v>
+        <v>4854.722370151818</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
@@ -3452,66 +3510,66 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12">
-        <v>4740.754834468833</v>
+        <v>4737.95107948982</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13">
-        <v>4260.737987822766</v>
+        <v>4260.422823120769</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14">
-        <v>95.50059516486002</v>
+        <v>95.49982787020204</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>4854.731019167153</v>
+        <v>4854.722370151818</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -3522,66 +3580,66 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
       </c>
       <c r="D17">
-        <v>4621.907529600363</v>
+        <v>4618.904679773948</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18">
-        <v>4133.549380028947</v>
+        <v>4133.498062660859</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19">
-        <v>92.64229592541933</v>
+        <v>92.64095886599212</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20">
-        <v>4709.138331956709</v>
+        <v>4709.125925120105</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -3592,66 +3650,66 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
       </c>
       <c r="D22">
-        <v>4621.907529600363</v>
+        <v>4618.904679773948</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23">
-        <v>4133.549380028947</v>
+        <v>4133.498062660859</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24">
-        <v>92.64229592541933</v>
+        <v>92.64095886599212</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
       </c>
       <c r="D25">
-        <v>4709.138331956709</v>
+        <v>4709.125925120105</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>21</v>
@@ -3662,66 +3720,66 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
       </c>
       <c r="D27">
-        <v>4621.907529600363</v>
+        <v>4618.904679773948</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28">
-        <v>4133.549380028947</v>
+        <v>4133.498062660859</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29">
-        <v>92.64229592541933</v>
+        <v>92.64095886599212</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
         <v>20</v>
       </c>
       <c r="D30">
-        <v>4709.138331956709</v>
+        <v>4709.125925120105</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
@@ -3742,7 +3800,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
@@ -3779,16 +3837,16 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>4739.996991807391</v>
+        <v>4739.910466424466</v>
       </c>
       <c r="C3">
-        <v>4073.582342654504</v>
+        <v>4074.55451655588</v>
       </c>
       <c r="D3">
-        <v>5515.670508546701</v>
+        <v>5513.336989191947</v>
       </c>
       <c r="E3">
-        <v>7.735681898531611</v>
+        <v>7.738761185096656</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3796,16 +3854,16 @@
         <v>0.8</v>
       </c>
       <c r="B4">
-        <v>4740.754834468833</v>
+        <v>4737.95107948982</v>
       </c>
       <c r="C4">
-        <v>4057.201505032894</v>
+        <v>4058.744036322647</v>
       </c>
       <c r="D4">
-        <v>5545.702306261544</v>
+        <v>5530.788783149665</v>
       </c>
       <c r="E4">
-        <v>7.91774161569511</v>
+        <v>7.879728401444697</v>
       </c>
     </row>
   </sheetData>
@@ -3820,10 +3878,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>4</v>
@@ -3843,19 +3901,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>4740.754834468833</v>
+        <v>4737.95107948982</v>
       </c>
       <c r="D2">
-        <v>4057.201505032894</v>
+        <v>4058.744036322647</v>
       </c>
       <c r="E2">
-        <v>5545.702306261544</v>
+        <v>5530.788783149665</v>
       </c>
       <c r="F2">
-        <v>7.91774161569511</v>
+        <v>7.879728401444697</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3863,19 +3921,19 @@
         <v>0.76</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>4739.376149412801</v>
+        <v>4737.041982984322</v>
       </c>
       <c r="D3">
-        <v>4114.297537506432</v>
+        <v>4110.144510858054</v>
       </c>
       <c r="E3">
-        <v>5476.614809800862</v>
+        <v>5464.535850016318</v>
       </c>
       <c r="F3">
-        <v>7.338779835986881</v>
+        <v>7.296104808137388</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3883,19 +3941,19 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>4737.923134306791</v>
+        <v>4736.696781531018</v>
       </c>
       <c r="D4">
-        <v>4314.697258683934</v>
+        <v>4315.190787569998</v>
       </c>
       <c r="E4">
-        <v>5273.513454289891</v>
+        <v>5263.412418503937</v>
       </c>
       <c r="F4">
-        <v>5.152459723363281</v>
+        <v>5.086590765855958</v>
       </c>
     </row>
   </sheetData>
@@ -3913,22 +3971,22 @@
         <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3936,7 +3994,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2">
         <v>0.0835</v>
@@ -3948,15 +4006,15 @@
         <v>1.177479106404468</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>1.1</v>
@@ -3968,15 +4026,15 @@
         <v>1.205395769474916</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>1.3</v>
@@ -3988,15 +4046,15 @@
         <v>1.672356915945362</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>1.15</v>
@@ -4008,15 +4066,15 @@
         <v>1.315127221128319</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>1.25</v>
@@ -4028,15 +4086,15 @@
         <v>1.548615584577687</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>1.4</v>
@@ -4048,7 +4106,7 @@
         <v>1.933797301790597</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="83">
   <si>
     <t>pharma_scenario</t>
   </si>
@@ -196,13 +196,25 @@
     <t>interpretation</t>
   </si>
   <si>
-    <t>perfect correlation (study default, upper bound)</t>
-  </si>
-  <si>
-    <t>Rodrigues et al. 2018 measured median for country consumption-based accounts</t>
-  </si>
-  <si>
-    <t>independence (lower bound; Rodrigues et al. show this understates uncertainty)</t>
+    <t>sigma_used</t>
+  </si>
+  <si>
+    <t>mrio_block_cv_if_not_recalibrated_pct</t>
+  </si>
+  <si>
+    <t>median_group_cv_pct</t>
+  </si>
+  <si>
+    <t>max_group_cv_pct</t>
+  </si>
+  <si>
+    <t>perfect correlation (study default). Rodrigues (2016): the only value consistent with holding a known aggregate uncertainty</t>
+  </si>
+  <si>
+    <t>Rodrigues et al. (2018) measured median correlation between country consumption-based accounts</t>
+  </si>
+  <si>
+    <t>independence. Rodrigues et al. (2018) show this understates aggregate uncertainty by about half unless the spread is re-solved, as it is here</t>
   </si>
   <si>
     <t>distribution</t>
@@ -934,37 +946,37 @@
         <v>4259.384222540152</v>
       </c>
       <c r="E8">
-        <v>2393.748478938714</v>
+        <v>2394.908968344549</v>
       </c>
       <c r="F8">
-        <v>2414.936337310955</v>
+        <v>2415.181959479386</v>
       </c>
       <c r="G8">
-        <v>247.4925726876774</v>
+        <v>246.7217437541242</v>
       </c>
       <c r="H8">
-        <v>10.2484098178448</v>
+        <v>10.21545158474549</v>
       </c>
       <c r="I8">
-        <v>1987.39825231248</v>
+        <v>1988.380728169875</v>
       </c>
       <c r="J8">
-        <v>2176.325512673546</v>
+        <v>2176.436756889149</v>
       </c>
       <c r="K8">
-        <v>2653.893697847422</v>
+        <v>2651.83580095395</v>
       </c>
       <c r="L8">
-        <v>2954.056371768522</v>
+        <v>2957.513889612693</v>
       </c>
       <c r="M8">
-        <v>-16.97547717320712</v>
+        <v>-16.97468444722061</v>
       </c>
       <c r="N8">
-        <v>23.40713311192262</v>
+        <v>23.49170380605479</v>
       </c>
       <c r="O8">
-        <v>0.05582481553875492</v>
+        <v>0.04581725841684954</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -981,37 +993,37 @@
         <v>95.50495307556376</v>
       </c>
       <c r="E9">
-        <v>70.9779644847637</v>
+        <v>70.93059693974409</v>
       </c>
       <c r="F9">
-        <v>71.46898782079096</v>
+        <v>71.39291097226587</v>
       </c>
       <c r="G9">
-        <v>15.36784329407484</v>
+        <v>15.36356734298192</v>
       </c>
       <c r="H9">
-        <v>21.50281368558042</v>
+        <v>21.51973793161374</v>
       </c>
       <c r="I9">
-        <v>45.97856629851675</v>
+        <v>45.89971341780939</v>
       </c>
       <c r="J9">
-        <v>54.38937292011902</v>
+        <v>54.32077757573968</v>
       </c>
       <c r="K9">
-        <v>88.20293555976561</v>
+        <v>88.12179082638386</v>
       </c>
       <c r="L9">
-        <v>100.7961201871926</v>
+        <v>100.7140278958918</v>
       </c>
       <c r="M9">
-        <v>-35.22135125699945</v>
+        <v>-35.28926105499798</v>
       </c>
       <c r="N9">
-        <v>42.01044073168616</v>
+        <v>41.98953941054364</v>
       </c>
       <c r="O9">
-        <v>0.09775313726266661</v>
+        <v>0.1223770346792459</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1028,37 +1040,37 @@
         <v>4855.460127817173</v>
       </c>
       <c r="E10">
-        <v>3966.317150993645</v>
+        <v>3963.387645344955</v>
       </c>
       <c r="F10">
-        <v>3990.466953239234</v>
+        <v>3991.418522868724</v>
       </c>
       <c r="G10">
-        <v>608.5719604512628</v>
+        <v>609.0923204060258</v>
       </c>
       <c r="H10">
-        <v>15.25064528995181</v>
+        <v>15.26004644504824</v>
       </c>
       <c r="I10">
-        <v>2945.500175850812</v>
+        <v>2945.181514566571</v>
       </c>
       <c r="J10">
-        <v>3343.401580152713</v>
+        <v>3346.280228853972</v>
       </c>
       <c r="K10">
-        <v>4628.117920975161</v>
+        <v>4634.98342929957</v>
       </c>
       <c r="L10">
-        <v>5208.729260629635</v>
+        <v>5205.462177367764</v>
       </c>
       <c r="M10">
-        <v>-25.73714950876021</v>
+        <v>-25.6902988526565</v>
       </c>
       <c r="N10">
-        <v>31.32407375251724</v>
+        <v>31.3387092852661</v>
       </c>
       <c r="O10">
-        <v>0.0863540884311406</v>
+        <v>0.06964773696313153</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1075,37 +1087,37 @@
         <v>259.4180916719396</v>
       </c>
       <c r="E11">
-        <v>216.3333926896765</v>
+        <v>216.2758463520067</v>
       </c>
       <c r="F11">
-        <v>217.4884476366681</v>
+        <v>217.4182171194676</v>
       </c>
       <c r="G11">
-        <v>29.17034517859893</v>
+        <v>29.17654973377195</v>
       </c>
       <c r="H11">
-        <v>13.41236534426432</v>
+        <v>13.41955155383319</v>
       </c>
       <c r="I11">
-        <v>167.2198895987555</v>
+        <v>167.3927420411474</v>
       </c>
       <c r="J11">
-        <v>186.3742805490548</v>
+        <v>186.1301871710449</v>
       </c>
       <c r="K11">
-        <v>248.3732595722919</v>
+        <v>248.3131623653739</v>
       </c>
       <c r="L11">
-        <v>274.9911097209454</v>
+        <v>275.0733702012921</v>
       </c>
       <c r="M11">
-        <v>-22.70269165582438</v>
+        <v>-22.60220229645898</v>
       </c>
       <c r="N11">
-        <v>27.11449966275508</v>
+        <v>27.18635707178669</v>
       </c>
       <c r="O11">
-        <v>0.05574829518999678</v>
+        <v>0.07522927821663197</v>
       </c>
     </row>
   </sheetData>
@@ -2701,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0.07897999999999999</v>
+        <v>0.07765</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2735,13 +2747,13 @@
         <v>44</v>
       </c>
       <c r="D61">
-        <v>0.00056</v>
+        <v>0.00039</v>
       </c>
       <c r="E61">
-        <v>0.34987</v>
+        <v>0.35077</v>
       </c>
       <c r="F61">
-        <v>0.57059</v>
+        <v>0.57119</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2758,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.64957</v>
+        <v>0.64884</v>
       </c>
       <c r="F62">
-        <v>0.35043</v>
+        <v>0.35116</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2795,10 +2807,10 @@
         <v>47</v>
       </c>
       <c r="D64">
-        <v>0.99944</v>
+        <v>0.99961</v>
       </c>
       <c r="E64">
-        <v>0.00056</v>
+        <v>0.00039</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -2815,10 +2827,10 @@
         <v>39</v>
       </c>
       <c r="D65">
-        <v>0.2459</v>
+        <v>0.24732</v>
       </c>
       <c r="E65">
-        <v>0.7541</v>
+        <v>0.75268</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2915,13 +2927,13 @@
         <v>44</v>
       </c>
       <c r="D70">
-        <v>0.7541</v>
+        <v>0.75268</v>
       </c>
       <c r="E70">
-        <v>0.19259</v>
+        <v>0.19274</v>
       </c>
       <c r="F70">
-        <v>0.05331</v>
+        <v>0.05458</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2938,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.05331</v>
+        <v>0.05458</v>
       </c>
       <c r="F71">
-        <v>0.94669</v>
+        <v>0.94542</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2995,10 +3007,10 @@
         <v>39</v>
       </c>
       <c r="D74">
-        <v>0.73628</v>
+        <v>0.73472</v>
       </c>
       <c r="E74">
-        <v>0.26372</v>
+        <v>0.26528</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3095,13 +3107,13 @@
         <v>44</v>
       </c>
       <c r="D79">
-        <v>0.26372</v>
+        <v>0.26528</v>
       </c>
       <c r="E79">
-        <v>0.50845</v>
+        <v>0.50619</v>
       </c>
       <c r="F79">
-        <v>0.22783</v>
+        <v>0.22853</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3118,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0.22783</v>
+        <v>0.22853</v>
       </c>
       <c r="F80">
-        <v>0.77217</v>
+        <v>0.77147</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3178,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0.00756</v>
+        <v>0.0074</v>
       </c>
       <c r="F83">
-        <v>0.2461</v>
+        <v>0.24687</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3255,13 +3267,13 @@
         <v>43</v>
       </c>
       <c r="D87">
-        <v>0.3145</v>
+        <v>0.31684</v>
       </c>
       <c r="E87">
-        <v>0.6122300000000001</v>
+        <v>0.61004</v>
       </c>
       <c r="F87">
-        <v>0.04669</v>
+        <v>0.04662</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3275,13 +3287,13 @@
         <v>44</v>
       </c>
       <c r="D88">
-        <v>0.6639</v>
+        <v>0.66143</v>
       </c>
       <c r="E88">
-        <v>0.08562</v>
+        <v>0.08783000000000001</v>
       </c>
       <c r="F88">
-        <v>0.02306</v>
+        <v>0.02265</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3301,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0.00034</v>
+        <v>0.00032</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3335,13 +3347,13 @@
         <v>47</v>
       </c>
       <c r="D91">
-        <v>0.0216</v>
+        <v>0.02173</v>
       </c>
       <c r="E91">
-        <v>0.29459</v>
+        <v>0.29473</v>
       </c>
       <c r="F91">
-        <v>0.68381</v>
+        <v>0.68354</v>
       </c>
     </row>
   </sheetData>
@@ -3873,10 +3885,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -3895,65 +3907,113 @@
       <c r="F1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>4737.95107948982</v>
+        <v>4735.238652316206</v>
       </c>
       <c r="D2">
-        <v>4058.744036322647</v>
+        <v>4067.87440236864</v>
       </c>
       <c r="E2">
-        <v>5530.788783149665</v>
+        <v>5527.246191369643</v>
       </c>
       <c r="F2">
-        <v>7.879728401444697</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>7.850983649240221</v>
+      </c>
+      <c r="G2">
+        <v>0.08335500138817992</v>
+      </c>
+      <c r="H2">
+        <v>8.379058580808772</v>
+      </c>
+      <c r="I2">
+        <v>8.370461611866567</v>
+      </c>
+      <c r="J2">
+        <v>26.21762709540243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>0.76</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>4737.041982984322</v>
+        <v>4740.008729028685</v>
       </c>
       <c r="D3">
-        <v>4110.144510858054</v>
+        <v>4074.836801493152</v>
       </c>
       <c r="E3">
-        <v>5464.535850016318</v>
+        <v>5531.763984376011</v>
       </c>
       <c r="F3">
-        <v>7.296104808137388</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>7.830387265994849</v>
+      </c>
+      <c r="G3">
+        <v>0.09153341947671678</v>
+      </c>
+      <c r="H3">
+        <v>7.596226723438768</v>
+      </c>
+      <c r="I3">
+        <v>9.194867053946274</v>
+      </c>
+      <c r="J3">
+        <v>26.21762709540243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>4736.696781531018</v>
+        <v>4772.925747306048</v>
       </c>
       <c r="D4">
-        <v>4315.190787569998</v>
+        <v>4120.418516667922</v>
       </c>
       <c r="E4">
-        <v>5263.412418503937</v>
+        <v>5575.416446522172</v>
       </c>
       <c r="F4">
-        <v>5.086590765855958</v>
+        <v>7.721936432399692</v>
+      </c>
+      <c r="G4">
+        <v>0.1606866915652795</v>
+      </c>
+      <c r="H4">
+        <v>4.270567387887708</v>
+      </c>
+      <c r="I4">
+        <v>16.1525017673782</v>
+      </c>
+      <c r="J4">
+        <v>26.21762709540243</v>
       </c>
     </row>
   </sheetData>
@@ -3971,22 +4031,22 @@
         <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3994,7 +4054,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D2">
         <v>0.0835</v>
@@ -4006,15 +4066,15 @@
         <v>1.177479106404468</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>1.1</v>
@@ -4026,15 +4086,15 @@
         <v>1.205395769474916</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>1.3</v>
@@ -4046,15 +4106,15 @@
         <v>1.672356915945362</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>1.15</v>
@@ -4066,15 +4126,15 @@
         <v>1.315127221128319</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C6">
         <v>1.25</v>
@@ -4086,15 +4146,15 @@
         <v>1.548615584577687</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C7">
         <v>1.4</v>
@@ -4106,7 +4166,7 @@
         <v>1.933797301790597</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
+++ b/data/gold/results/04_uncertainty_lenzen_ieooc/uncertainty_summary.xlsx
@@ -661,40 +661,40 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>4713.367605953854</v>
+        <v>4712.417605953854</v>
       </c>
       <c r="E2">
-        <v>4734.725238865476</v>
+        <v>4733.659773313824</v>
       </c>
       <c r="F2">
-        <v>4750.935562516105</v>
+        <v>4749.952065897599</v>
       </c>
       <c r="G2">
-        <v>373.7878496002326</v>
+        <v>373.7860346835424</v>
       </c>
       <c r="H2">
-        <v>7.867668266211418</v>
+        <v>7.869259089310578</v>
       </c>
       <c r="I2">
-        <v>4064.511469512162</v>
+        <v>4063.643366769841</v>
       </c>
       <c r="J2">
-        <v>4382.869614413962</v>
+        <v>4381.827282506621</v>
       </c>
       <c r="K2">
-        <v>5119.360556791389</v>
+        <v>5118.405571889963</v>
       </c>
       <c r="L2">
-        <v>5532.19898998981</v>
+        <v>5531.252639583388</v>
       </c>
       <c r="M2">
-        <v>-14.15528326441829</v>
+        <v>-14.15430002640293</v>
       </c>
       <c r="N2">
-        <v>16.8430840416713</v>
+        <v>16.84939147435189</v>
       </c>
       <c r="O2">
-        <v>0.03587953771436504</v>
+        <v>0.0359398247900479</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -896,40 +896,40 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>4713.367605953854</v>
+        <v>4712.417605953854</v>
       </c>
       <c r="E7">
-        <v>3605.390020206104</v>
+        <v>3604.390559468272</v>
       </c>
       <c r="F7">
-        <v>3640.936341722425</v>
+        <v>3639.952845103919</v>
       </c>
       <c r="G7">
-        <v>388.6479453529622</v>
+        <v>388.6468956536662</v>
       </c>
       <c r="H7">
-        <v>10.67439550918113</v>
+        <v>10.67725083791767</v>
       </c>
       <c r="I7">
-        <v>2980.086319286984</v>
+        <v>2979.229694469976</v>
       </c>
       <c r="J7">
-        <v>3263.73190929662</v>
+        <v>3262.701520404984</v>
       </c>
       <c r="K7">
-        <v>4020.695496597223</v>
+        <v>4019.713341013183</v>
       </c>
       <c r="L7">
-        <v>4502.750577485003</v>
+        <v>4501.663493507316</v>
       </c>
       <c r="M7">
-        <v>-17.34357995708253</v>
+        <v>-17.34442632350366</v>
       </c>
       <c r="N7">
-        <v>24.88941701867808</v>
+        <v>24.89388758612805</v>
       </c>
       <c r="O7">
-        <v>0.0313307960326539</v>
+        <v>0.03132667160181331</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1149,7 +1149,7 @@
         <v>28</v>
       </c>
       <c r="C2">
-        <v>78.75829747123008</v>
+        <v>78.75929022214825</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1160,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="C3">
-        <v>0.09336762509660612</v>
+        <v>0.09336880199857733</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1171,7 +1171,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>0.008634896218265452</v>
+        <v>0.007374501787399149</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1182,7 +1182,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>0.001952497422454561</v>
+        <v>0.001952522033748496</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1193,7 +1193,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>5.121129957228417</v>
+        <v>5.121194509239194</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1204,7 +1204,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>6.727158804026204</v>
+        <v>6.727243600083177</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1215,7 +1215,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>9.289458748777989</v>
+        <v>9.289575842709654</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3391,7 +3391,7 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>4737.95107948982</v>
+        <v>4736.901601366199</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4737.95107948982</v>
+        <v>4736.901601366199</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>17</v>
       </c>
       <c r="D12">
-        <v>4737.95107948982</v>
+        <v>4736.901601366199</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>4618.904679773948</v>
+        <v>4617.860374761685</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>17</v>
       </c>
       <c r="D22">
-        <v>4618.904679773948</v>
+        <v>4617.860374761685</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>4618.904679773948</v>
+        <v>4617.860374761685</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3832,16 +3832,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4741.353433368069</v>
+        <v>4740.432219635997</v>
       </c>
       <c r="C2">
-        <v>4096.493530952253</v>
+        <v>4095.684785594958</v>
       </c>
       <c r="D2">
-        <v>5492.97103312192</v>
+        <v>5492.347473800488</v>
       </c>
       <c r="E2">
-        <v>7.485350890554811</v>
+        <v>7.486835308286129</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3849,16 +3849,16 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>4739.910466424466</v>
+        <v>4738.939297601524</v>
       </c>
       <c r="C3">
-        <v>4074.55451655588</v>
+        <v>4073.411557591191</v>
       </c>
       <c r="D3">
-        <v>5513.336989191947</v>
+        <v>5512.102269628917</v>
       </c>
       <c r="E3">
-        <v>7.738761185096656</v>
+        <v>7.740309384720568</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3866,16 +3866,16 @@
         <v>0.8</v>
       </c>
       <c r="B4">
-        <v>4737.95107948982</v>
+        <v>4736.901601366199</v>
       </c>
       <c r="C4">
-        <v>4058.744036322647</v>
+        <v>4057.526533610328</v>
       </c>
       <c r="D4">
-        <v>5530.788783149665</v>
+        <v>5529.556135599134</v>
       </c>
       <c r="E4">
-        <v>7.879728401444697</v>
+        <v>7.881310646973933</v>
       </c>
     </row>
   </sheetData>
@@ -3928,16 +3928,16 @@
         <v>62</v>
       </c>
       <c r="C2">
-        <v>4735.238652316206</v>
+        <v>4734.20181449759</v>
       </c>
       <c r="D2">
-        <v>4067.87440236864</v>
+        <v>4067.039734534132</v>
       </c>
       <c r="E2">
-        <v>5527.246191369643</v>
+        <v>5526.229517058416</v>
       </c>
       <c r="F2">
-        <v>7.850983649240221</v>
+        <v>7.852589550926811</v>
       </c>
       <c r="G2">
         <v>0.08335500138817992</v>
@@ -3960,16 +3960,16 @@
         <v>63</v>
       </c>
       <c r="C3">
-        <v>4740.008729028685</v>
+        <v>4738.951934274523</v>
       </c>
       <c r="D3">
-        <v>4074.836801493152</v>
+        <v>4074.011023264848</v>
       </c>
       <c r="E3">
-        <v>5531.763984376011</v>
+        <v>5530.747615978656</v>
       </c>
       <c r="F3">
-        <v>7.830387265994849</v>
+        <v>7.83198521383204</v>
       </c>
       <c r="G3">
         <v>0.09153341947671678</v>
@@ -3992,16 +3992,16 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>4772.925747306048</v>
+        <v>4771.855590610307</v>
       </c>
       <c r="D4">
-        <v>4120.418516667922</v>
+        <v>4119.5237639701</v>
       </c>
       <c r="E4">
-        <v>5575.416446522172</v>
+        <v>5574.023936591538</v>
       </c>
       <c r="F4">
-        <v>7.721936432399692</v>
+        <v>7.723488308479567</v>
       </c>
       <c r="G4">
         <v>0.1606866915652795</v>
